--- a/p6_deployment/data/argentina/predicciones.xlsx
+++ b/p6_deployment/data/argentina/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jNQN0abb</t>
+          <t>80hEjzhl</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45439.875</v>
+        <v>45458.75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>atl  tucuman</t>
+          <t>huracan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>platense</t>
+          <t>ind  rivadavia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,64 +585,204 @@
         <v>61</v>
       </c>
       <c r="G2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5696460056964601</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2718025227180252</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1585514715855147</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05118334759053322</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>1.30638852672751</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ChkVnhiD</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45458.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>atl  tucuman</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>defensa y justicia</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>61</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4931894569255263</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2770564302140457</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2297541128604281</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.06158029550729749</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2991182851373308</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3871825052785184</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3136992095841509</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1101260750644728</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1101260750644728</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.3871825052785184</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.1</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>19.35912526392592</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>19.35912526392592</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>UHaVQ4y2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45459.54166666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>river plate</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>talleres cordoba</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.4736842105263159</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.3157894736842106</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.05555555555555536</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="O4" t="n">
+        <v>0.4028577852796484</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.07065718925890503</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5264850254614466</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>0.4334187379609695</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2895297263314668</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.2770515357075635</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>-0.04026547256534635</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.04026547256534635</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.5665812620390305</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.4735149745385534</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.1</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>28.32906310195152</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>28.32906310195152</v>
+      <c r="Y4" t="n">
+        <v>23.67574872692767</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>23.67574872692767</v>
       </c>
     </row>
   </sheetData>
